--- a/Financial Analysis/FCEL.xlsx
+++ b/Financial Analysis/FCEL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8F88124-3411-4095-93CE-B8CAB9C6CB5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C544E6D0-D9D7-41DB-B4A6-EF9C82156C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{42CD1468-76D2-4D3B-B2D7-BE92B4A8E026}"/>
   </bookViews>
@@ -400,7 +400,7 @@
     <t>NPV (FCF)</t>
   </si>
   <si>
-    <t>Heavily undervalued</t>
+    <t>Fairly valued</t>
   </si>
 </sst>
 </file>
@@ -943,14 +943,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>3.72</v>
+        <v>5.6</v>
       </c>
       <c r="E3" s="4">
-        <v>45772</v>
+        <v>45804</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45772</v>
+        <v>45804</v>
       </c>
       <c r="G3" s="4">
         <v>45817</v>
@@ -973,7 +973,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>78.492000000000004</v>
+        <v>118.16</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>-49.507999999999996</v>
+        <v>-9.8400000000000034</v>
       </c>
     </row>
   </sheetData>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="AS47" s="5">
         <f>Main!D3</f>
-        <v>3.72</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="48" spans="2:45" x14ac:dyDescent="0.3">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="AS48" s="11">
         <f>AS46/AS47-1</f>
-        <v>0.5117314448778445</v>
+        <v>4.2216026688539632E-3</v>
       </c>
     </row>
     <row r="49" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -11338,7 +11338,7 @@
       </c>
       <c r="AS114" s="5">
         <f>Main!D3</f>
-        <v>3.72</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="115" spans="2:45" x14ac:dyDescent="0.3">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="AS115" s="11">
         <f>AS113/AS114-1</f>
-        <v>1.3643763443985364</v>
+        <v>0.57062142877902788</v>
       </c>
     </row>
     <row r="116" spans="2:45" x14ac:dyDescent="0.3">

--- a/Financial Analysis/FCEL.xlsx
+++ b/Financial Analysis/FCEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BEC6E43-67D1-4306-9485-85FAC5BDCBD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2797ED0-5D79-4DD7-99AF-F2E0FCC7B3FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{42CD1468-76D2-4D3B-B2D7-BE92B4A8E026}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="137">
   <si>
     <t>FCEL</t>
   </si>
@@ -434,6 +434,9 @@
   </si>
   <si>
     <t>Price to book</t>
+  </si>
+  <si>
+    <t>Fairly valued</t>
   </si>
 </sst>
 </file>
@@ -1017,7 +1020,7 @@
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45927</v>
+        <v>45928</v>
       </c>
       <c r="G3" s="4">
         <v>45912</v>
@@ -12691,6 +12694,9 @@
       <c r="T130">
         <v>0.7</v>
       </c>
+      <c r="AS130" s="7" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="131" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B131" t="s">

--- a/Financial Analysis/FCEL.xlsx
+++ b/Financial Analysis/FCEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2797ED0-5D79-4DD7-99AF-F2E0FCC7B3FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E70F16-F602-4E9B-9680-5416C98E4E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{42CD1468-76D2-4D3B-B2D7-BE92B4A8E026}"/>
   </bookViews>
@@ -1013,17 +1013,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>7.85</v>
+        <v>7.81</v>
       </c>
       <c r="E3" s="4">
-        <v>45927</v>
+        <v>45959</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45928</v>
+        <v>45959</v>
       </c>
       <c r="G3" s="4">
-        <v>45912</v>
+        <v>46009</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>191.54</v>
+        <v>190.56399999999999</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>90.640000000000015</v>
+        <v>89.664000000000016</v>
       </c>
     </row>
   </sheetData>
@@ -6913,7 +6913,7 @@
       </c>
       <c r="AS48" s="5">
         <f>Main!D3</f>
-        <v>7.85</v>
+        <v>7.81</v>
       </c>
     </row>
     <row r="49" spans="2:45" x14ac:dyDescent="0.3">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="AS49" s="11">
         <f>AS47/AS48-1</f>
-        <v>-0.99110072258398429</v>
+        <v>-0.99105514369837089</v>
       </c>
     </row>
     <row r="50" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="AS128" s="5">
         <f>Main!D3</f>
-        <v>7.85</v>
+        <v>7.81</v>
       </c>
     </row>
     <row r="129" spans="2:45" x14ac:dyDescent="0.3">
@@ -12669,7 +12669,7 @@
       </c>
       <c r="AS129" s="11">
         <f>AS127/AS128-1</f>
-        <v>-4.329644050409831E-2</v>
+        <v>-3.8396550314618638E-2</v>
       </c>
     </row>
     <row r="130" spans="2:45" x14ac:dyDescent="0.3">

--- a/Financial Analysis/FCEL.xlsx
+++ b/Financial Analysis/FCEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{246FE059-1540-4718-9114-9E9AB2C1DF26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68374F49-73D4-418A-87F8-36854E52A395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{42CD1468-76D2-4D3B-B2D7-BE92B4A8E026}"/>
   </bookViews>
@@ -448,7 +448,7 @@
     <t>Q426</t>
   </si>
   <si>
-    <t>Heavily overvalued</t>
+    <t>Slightly undervalued</t>
   </si>
 </sst>
 </file>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>46052</v>
+        <v>46078</v>
       </c>
       <c r="G3" s="4">
         <v>46091</v>
@@ -6515,8 +6515,8 @@
         <v>65</v>
       </c>
       <c r="AW44" s="6">
-        <f>NPV(AW43,AI32:EV32)</f>
-        <v>-38.094085836629063</v>
+        <f>NPV(AW43,AJ32:EV32)</f>
+        <v>148.13462386297562</v>
       </c>
     </row>
     <row r="45" spans="2:49" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="AW46" s="6">
         <f>AW44+AW45</f>
-        <v>172.70591416337101</v>
+        <v>358.93462386297568</v>
       </c>
     </row>
     <row r="47" spans="2:49" x14ac:dyDescent="0.3">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="AW47" s="5">
         <f>AW46/AS33</f>
-        <v>3.6206690600287419</v>
+        <v>7.5248348818233888</v>
       </c>
     </row>
     <row r="48" spans="2:49" x14ac:dyDescent="0.3">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="AW49" s="11">
         <f>AW47/AW48-1</f>
-        <v>-0.56586701918120608</v>
+        <v>-9.7741620884485791E-2</v>
       </c>
     </row>
     <row r="50" spans="2:49" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -7483,7 +7483,7 @@
         <v>71</v>
       </c>
       <c r="AW50" s="7" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="51" spans="2:49" x14ac:dyDescent="0.3">
@@ -12996,8 +12996,8 @@
         <v>123</v>
       </c>
       <c r="AW124" s="6">
-        <f>NPV(AW43,AI120:EP120)</f>
-        <v>143.44831791687216</v>
+        <f>NPV(AW43,AJ120:EP120)</f>
+        <v>287.46211606689667</v>
       </c>
     </row>
     <row r="125" spans="2:146" x14ac:dyDescent="0.3">
@@ -13057,7 +13057,7 @@
       </c>
       <c r="AW126" s="6">
         <f>AW124+AW125</f>
-        <v>354.24831791687222</v>
+        <v>498.26211606689674</v>
       </c>
     </row>
     <row r="127" spans="2:146" x14ac:dyDescent="0.3">
@@ -13087,7 +13087,7 @@
       </c>
       <c r="AW127" s="5">
         <f>AW126/AS33</f>
-        <v>7.4265894741482645</v>
+        <v>10.445746668069113</v>
       </c>
     </row>
     <row r="128" spans="2:146" x14ac:dyDescent="0.3">
@@ -13148,7 +13148,7 @@
       </c>
       <c r="AW129" s="11">
         <f>AW127/AW128-1</f>
-        <v>-0.10952164578557977</v>
+        <v>0.25248761008022935</v>
       </c>
     </row>
     <row r="130" spans="2:49" x14ac:dyDescent="0.3">
@@ -13174,7 +13174,7 @@
         <v>0.7</v>
       </c>
       <c r="AW130" s="7" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="131" spans="2:49" x14ac:dyDescent="0.3">
